--- a/docs/eu/StructureDefinition-Quantity-eu-lab.xlsx
+++ b/docs/eu/StructureDefinition-Quantity-eu-lab.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-15T17:10:39+02:00</t>
+    <t>2026-03-15T18:11:06+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/eu/StructureDefinition-Quantity-eu-lab.xlsx
+++ b/docs/eu/StructureDefinition-Quantity-eu-lab.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.0.1</t>
+    <t>0.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-15T18:11:06+02:00</t>
+    <t>2026-03-15T21:22:52+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
